--- a/gdcdictionary/xlsx/nodes_schema_impowr.xlsx
+++ b/gdcdictionary/xlsx/nodes_schema_impowr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\davidc\git\wf\dcfdictionary\gdcdictionary\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08126013-3BA8-4704-93FE-C6B6F40A9193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B30A35-28A9-49B8-AF79-7995BE38DC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23100" yWindow="96" windowWidth="22416" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17200" yWindow="-19710" windowWidth="28800" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nodes_impowr" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14492" uniqueCount="3579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14492" uniqueCount="3578">
   <si>
     <t>&lt;$schema&gt;</t>
   </si>
@@ -9238,9 +9238,6 @@
   </si>
   <si>
     <t>subjective_opiate_withdrawal_scale</t>
-  </si>
-  <si>
-    <t>Object</t>
   </si>
   <si>
     <t xml:space="preserve">Describes the patient baseline intensity of opioid withdrawal based on a 5-point scale of 16 symptoms. </t>
@@ -17159,7 +17156,7 @@
         <v>3049</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>3050</v>
+        <v>43</v>
       </c>
       <c r="F90" s="17" t="s">
         <v>45</v>
@@ -17174,7 +17171,7 @@
         <v>48</v>
       </c>
       <c r="J90" s="19" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="K90" s="3" t="s">
         <v>58</v>
@@ -17218,13 +17215,13 @@
         <v>25</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>3050</v>
+        <v>43</v>
       </c>
       <c r="F91" s="17" t="s">
         <v>45</v>
@@ -17239,7 +17236,7 @@
         <v>48</v>
       </c>
       <c r="J91" s="20" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>58</v>
@@ -17260,7 +17257,7 @@
         <v>228</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>77</v>
@@ -33474,10 +33471,10 @@
         <v>3048</v>
       </c>
       <c r="B1139" s="18" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="D1139" s="4" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="E1139" s="3" t="s">
         <v>173</v>
@@ -33488,10 +33485,10 @@
         <v>3048</v>
       </c>
       <c r="B1140" s="18" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="D1140" s="4" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="E1140" s="3" t="s">
         <v>173</v>
@@ -33502,10 +33499,10 @@
         <v>3048</v>
       </c>
       <c r="B1141" s="18" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="D1141" s="4" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="E1141" s="3" t="s">
         <v>174</v>
@@ -33516,10 +33513,10 @@
         <v>3048</v>
       </c>
       <c r="B1142" s="18" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="D1142" s="4" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="E1142" s="3" t="s">
         <v>174</v>
@@ -33530,10 +33527,10 @@
         <v>3048</v>
       </c>
       <c r="B1143" s="18" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="D1143" s="4" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="E1143" s="3" t="s">
         <v>174</v>
@@ -33544,10 +33541,10 @@
         <v>3048</v>
       </c>
       <c r="B1144" s="18" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="D1144" s="4" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="E1144" s="3" t="s">
         <v>174</v>
@@ -33558,10 +33555,10 @@
         <v>3048</v>
       </c>
       <c r="B1145" s="18" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="D1145" s="4" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="E1145" s="3" t="s">
         <v>174</v>
@@ -33572,10 +33569,10 @@
         <v>3048</v>
       </c>
       <c r="B1146" s="18" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="D1146" s="4" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="E1146" s="3" t="s">
         <v>174</v>
@@ -33586,10 +33583,10 @@
         <v>3048</v>
       </c>
       <c r="B1147" s="18" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="D1147" s="4" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="E1147" s="3" t="s">
         <v>174</v>
@@ -33600,10 +33597,10 @@
         <v>3048</v>
       </c>
       <c r="B1148" s="18" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="D1148" s="4" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="E1148" s="3" t="s">
         <v>174</v>
@@ -33614,10 +33611,10 @@
         <v>3048</v>
       </c>
       <c r="B1149" s="18" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="D1149" s="4" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="E1149" s="3" t="s">
         <v>174</v>
@@ -33628,10 +33625,10 @@
         <v>3048</v>
       </c>
       <c r="B1150" s="18" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="D1150" s="4" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="E1150" s="3" t="s">
         <v>174</v>
@@ -33642,10 +33639,10 @@
         <v>3048</v>
       </c>
       <c r="B1151" s="18" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="D1151" s="4" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="E1151" s="3" t="s">
         <v>174</v>
@@ -33656,10 +33653,10 @@
         <v>3048</v>
       </c>
       <c r="B1152" s="18" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="D1152" s="4" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="E1152" s="3" t="s">
         <v>174</v>
@@ -33670,10 +33667,10 @@
         <v>3048</v>
       </c>
       <c r="B1153" s="18" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="D1153" s="4" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="E1153" s="3" t="s">
         <v>174</v>
@@ -33684,10 +33681,10 @@
         <v>3048</v>
       </c>
       <c r="B1154" s="18" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="D1154" s="4" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="E1154" s="3" t="s">
         <v>174</v>
@@ -33698,10 +33695,10 @@
         <v>3048</v>
       </c>
       <c r="B1155" s="18" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="D1155" s="4" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="E1155" s="3" t="s">
         <v>174</v>
@@ -33712,10 +33709,10 @@
         <v>3048</v>
       </c>
       <c r="B1156" s="18" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="D1156" s="4" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="E1156" s="3" t="s">
         <v>174</v>
@@ -33726,10 +33723,10 @@
         <v>3048</v>
       </c>
       <c r="B1157" s="18" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="D1157" s="4" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="E1157" s="3" t="s">
         <v>175</v>
@@ -33737,10 +33734,10 @@
     </row>
     <row r="1158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1158" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1158" s="18" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="D1158" s="4" t="s">
         <v>3027</v>
@@ -33751,13 +33748,13 @@
     </row>
     <row r="1159" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1159" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1159" s="18" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="D1159" s="4" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="E1159" s="3" t="s">
         <v>173</v>
@@ -33765,13 +33762,13 @@
     </row>
     <row r="1160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1160" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1160" s="18" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="D1160" s="4" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="E1160" s="3" t="s">
         <v>177</v>
@@ -33779,13 +33776,13 @@
     </row>
     <row r="1161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1161" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1161" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="D1161" s="4" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="E1161" s="3" t="s">
         <v>177</v>
@@ -33793,10 +33790,10 @@
     </row>
     <row r="1162" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1162" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1162" s="18" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="D1162" s="4" t="s">
         <v>1679</v>
@@ -33807,13 +33804,13 @@
     </row>
     <row r="1163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1163" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1163" s="18" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="D1163" s="4" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="E1163" s="3" t="s">
         <v>177</v>
@@ -33821,13 +33818,13 @@
     </row>
     <row r="1164" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1164" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1164" s="18" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="D1164" s="4" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="E1164" s="3" t="s">
         <v>177</v>
@@ -33835,13 +33832,13 @@
     </row>
     <row r="1165" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1165" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1165" s="18" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="D1165" s="4" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="E1165" s="3" t="s">
         <v>177</v>
@@ -33849,13 +33846,13 @@
     </row>
     <row r="1166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1166" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1166" s="18" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="D1166" s="4" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="E1166" s="3" t="s">
         <v>177</v>
@@ -33863,13 +33860,13 @@
     </row>
     <row r="1167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1167" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1167" s="18" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="D1167" s="4" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="E1167" s="3" t="s">
         <v>177</v>
@@ -33877,13 +33874,13 @@
     </row>
     <row r="1168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1168" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1168" s="18" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="D1168" s="4" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="E1168" s="3" t="s">
         <v>177</v>
@@ -33891,13 +33888,13 @@
     </row>
     <row r="1169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1169" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1169" s="18" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="D1169" s="4" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="E1169" s="3" t="s">
         <v>177</v>
@@ -33905,13 +33902,13 @@
     </row>
     <row r="1170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1170" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1170" s="18" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="D1170" s="4" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="E1170" s="3" t="s">
         <v>177</v>
@@ -33919,10 +33916,10 @@
     </row>
     <row r="1171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1171" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1171" s="18" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="D1171" s="4" t="s">
         <v>1680</v>
@@ -33933,13 +33930,13 @@
     </row>
     <row r="1172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1172" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1172" s="18" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="D1172" s="4" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="E1172" s="3" t="s">
         <v>177</v>
@@ -33947,13 +33944,13 @@
     </row>
     <row r="1173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1173" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1173" s="18" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="D1173" s="4" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="E1173" s="3" t="s">
         <v>177</v>
@@ -33961,13 +33958,13 @@
     </row>
     <row r="1174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1174" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1174" s="18" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="D1174" s="4" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="E1174" s="3" t="s">
         <v>177</v>
@@ -33975,13 +33972,13 @@
     </row>
     <row r="1175" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1175" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1175" s="18" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="D1175" s="4" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="E1175" s="3" t="s">
         <v>177</v>
@@ -33989,13 +33986,13 @@
     </row>
     <row r="1176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1176" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1176" s="18" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="D1176" s="4" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="E1176" s="3" t="s">
         <v>177</v>
@@ -34003,13 +34000,13 @@
     </row>
     <row r="1177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1177" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1177" s="18" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="D1177" s="4" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="E1177" s="3" t="s">
         <v>177</v>
@@ -34017,13 +34014,13 @@
     </row>
     <row r="1178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1178" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1178" s="18" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="D1178" s="4" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="E1178" s="3" t="s">
         <v>177</v>
@@ -34031,13 +34028,13 @@
     </row>
     <row r="1179" spans="1:5" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1179" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1179" s="18" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="D1179" s="4" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="E1179" s="3" t="s">
         <v>173</v>
@@ -34045,10 +34042,10 @@
     </row>
     <row r="1180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1180" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1180" s="18" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="D1180" s="4" t="s">
         <v>1679</v>
@@ -34059,13 +34056,13 @@
     </row>
     <row r="1181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1181" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1181" s="18" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="D1181" s="4" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="E1181" s="3" t="s">
         <v>177</v>
@@ -34073,13 +34070,13 @@
     </row>
     <row r="1182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1182" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1182" s="18" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="D1182" s="4" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="E1182" s="3" t="s">
         <v>175</v>
@@ -34087,13 +34084,13 @@
     </row>
     <row r="1183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1183" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1183" s="18" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="D1183" s="4" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="E1183" s="3" t="s">
         <v>175</v>
@@ -34101,13 +34098,13 @@
     </row>
     <row r="1184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1184" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1184" s="18" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="D1184" s="4" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="E1184" s="3" t="s">
         <v>173</v>
@@ -34115,13 +34112,13 @@
     </row>
     <row r="1185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1185" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1185" s="18" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="D1185" s="4" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="E1185" s="3" t="s">
         <v>173</v>
@@ -34129,13 +34126,13 @@
     </row>
     <row r="1186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1186" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1186" s="18" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="D1186" s="4" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="E1186" s="3" t="s">
         <v>173</v>
@@ -34143,13 +34140,13 @@
     </row>
     <row r="1187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1187" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1187" s="18" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="D1187" s="4" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="E1187" s="3" t="s">
         <v>175</v>
@@ -34157,13 +34154,13 @@
     </row>
     <row r="1188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1188" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1188" s="18" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="D1188" s="4" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="E1188" s="3" t="s">
         <v>175</v>
@@ -34171,13 +34168,13 @@
     </row>
     <row r="1189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1189" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1189" s="18" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="D1189" s="4" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="E1189" s="3" t="s">
         <v>175</v>
@@ -34185,13 +34182,13 @@
     </row>
     <row r="1190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1190" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1190" s="18" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="D1190" s="4" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="E1190" s="3" t="s">
         <v>173</v>
@@ -34199,13 +34196,13 @@
     </row>
     <row r="1191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1191" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1191" s="18" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="D1191" s="4" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="E1191" s="3" t="s">
         <v>173</v>
@@ -34213,13 +34210,13 @@
     </row>
     <row r="1192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1192" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1192" s="18" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="D1192" s="4" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="E1192" s="3" t="s">
         <v>173</v>
@@ -34227,13 +34224,13 @@
     </row>
     <row r="1193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1193" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1193" s="18" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="D1193" s="4" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="E1193" s="3" t="s">
         <v>175</v>
@@ -34241,13 +34238,13 @@
     </row>
     <row r="1194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1194" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1194" s="18" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="D1194" s="4" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="E1194" s="3" t="s">
         <v>175</v>
@@ -34255,13 +34252,13 @@
     </row>
     <row r="1195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1195" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1195" s="18" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="D1195" s="4" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="E1195" s="3" t="s">
         <v>175</v>
@@ -34269,13 +34266,13 @@
     </row>
     <row r="1196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1196" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1196" s="18" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="D1196" s="4" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="E1196" s="3" t="s">
         <v>175</v>
@@ -34283,13 +34280,13 @@
     </row>
     <row r="1197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1197" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1197" s="18" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="D1197" s="4" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="E1197" s="3" t="s">
         <v>173</v>
@@ -34297,13 +34294,13 @@
     </row>
     <row r="1198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1198" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1198" s="18" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="D1198" s="4" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="E1198" s="3" t="s">
         <v>173</v>
@@ -34311,13 +34308,13 @@
     </row>
     <row r="1199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1199" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1199" s="18" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="D1199" s="4" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="E1199" s="3" t="s">
         <v>173</v>
@@ -34325,13 +34322,13 @@
     </row>
     <row r="1200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1200" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1200" s="18" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="D1200" s="4" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="E1200" s="3" t="s">
         <v>175</v>
@@ -34339,13 +34336,13 @@
     </row>
     <row r="1201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1201" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1201" s="18" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="D1201" s="4" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="E1201" s="3" t="s">
         <v>173</v>
@@ -34353,13 +34350,13 @@
     </row>
     <row r="1202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1202" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1202" s="18" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="D1202" s="4" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="E1202" s="3" t="s">
         <v>175</v>
@@ -34367,13 +34364,13 @@
     </row>
     <row r="1203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1203" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1203" s="18" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="D1203" s="4" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="E1203" s="3" t="s">
         <v>173</v>
@@ -34381,13 +34378,13 @@
     </row>
     <row r="1204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1204" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1204" s="18" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="D1204" s="4" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="E1204" s="3" t="s">
         <v>173</v>
@@ -34395,13 +34392,13 @@
     </row>
     <row r="1205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1205" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1205" s="18" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="D1205" s="4" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="E1205" s="3" t="s">
         <v>173</v>
@@ -34409,13 +34406,13 @@
     </row>
     <row r="1206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1206" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1206" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D1206" s="4" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="E1206" s="3" t="s">
         <v>175</v>
@@ -34423,13 +34420,13 @@
     </row>
     <row r="1207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1207" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1207" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D1207" s="4" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="E1207" s="3" t="s">
         <v>173</v>
@@ -34437,13 +34434,13 @@
     </row>
     <row r="1208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1208" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1208" s="18" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="D1208" s="4" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="E1208" s="3" t="s">
         <v>175</v>
@@ -34451,13 +34448,13 @@
     </row>
     <row r="1209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1209" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1209" s="18" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="D1209" s="4" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="E1209" s="3" t="s">
         <v>173</v>
@@ -34465,13 +34462,13 @@
     </row>
     <row r="1210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1210" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1210" s="18" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="D1210" s="4" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="E1210" s="3" t="s">
         <v>173</v>
@@ -34479,13 +34476,13 @@
     </row>
     <row r="1211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1211" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1211" s="18" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="D1211" s="4" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="E1211" s="3" t="s">
         <v>173</v>
@@ -34493,13 +34490,13 @@
     </row>
     <row r="1212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1212" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1212" s="18" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="D1212" s="4" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="E1212" s="3" t="s">
         <v>175</v>
@@ -34507,13 +34504,13 @@
     </row>
     <row r="1213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1213" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1213" s="18" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="D1213" s="4" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="E1213" s="3" t="s">
         <v>173</v>
@@ -34521,13 +34518,13 @@
     </row>
     <row r="1214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1214" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1214" s="18" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="D1214" s="4" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="E1214" s="3" t="s">
         <v>175</v>
@@ -34535,13 +34532,13 @@
     </row>
     <row r="1215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1215" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1215" s="18" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="D1215" s="4" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="E1215" s="3" t="s">
         <v>173</v>
@@ -34549,13 +34546,13 @@
     </row>
     <row r="1216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1216" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1216" s="18" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="D1216" s="4" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="E1216" s="3" t="s">
         <v>173</v>
@@ -34563,13 +34560,13 @@
     </row>
     <row r="1217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1217" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1217" s="18" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="D1217" s="4" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="E1217" s="3" t="s">
         <v>173</v>
@@ -34577,13 +34574,13 @@
     </row>
     <row r="1218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1218" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1218" s="18" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="D1218" s="4" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="E1218" s="3" t="s">
         <v>175</v>
@@ -34591,13 +34588,13 @@
     </row>
     <row r="1219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1219" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1219" s="18" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="D1219" s="4" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="E1219" s="3" t="s">
         <v>173</v>
@@ -34605,13 +34602,13 @@
     </row>
     <row r="1220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1220" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1220" s="18" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="D1220" s="4" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="E1220" s="3" t="s">
         <v>177</v>
@@ -34619,13 +34616,13 @@
     </row>
     <row r="1221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1221" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1221" s="18" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="D1221" s="4" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="E1221" s="3" t="s">
         <v>175</v>
@@ -34633,13 +34630,13 @@
     </row>
     <row r="1222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1222" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1222" s="18" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="D1222" s="4" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="E1222" s="3" t="s">
         <v>175</v>
@@ -34647,13 +34644,13 @@
     </row>
     <row r="1223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1223" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1223" s="18" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="D1223" s="4" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="E1223" s="3" t="s">
         <v>173</v>
@@ -34661,13 +34658,13 @@
     </row>
     <row r="1224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1224" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1224" s="18" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="D1224" s="4" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="E1224" s="3" t="s">
         <v>173</v>
@@ -34675,13 +34672,13 @@
     </row>
     <row r="1225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1225" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1225" s="18" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="D1225" s="4" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="E1225" s="3" t="s">
         <v>173</v>
@@ -34689,13 +34686,13 @@
     </row>
     <row r="1226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1226" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1226" s="18" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="D1226" s="4" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="E1226" s="3" t="s">
         <v>175</v>
@@ -34703,13 +34700,13 @@
     </row>
     <row r="1227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1227" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1227" s="18" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="D1227" s="4" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="E1227" s="3" t="s">
         <v>175</v>
@@ -34717,13 +34714,13 @@
     </row>
     <row r="1228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1228" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1228" s="18" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="D1228" s="4" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="E1228" s="3" t="s">
         <v>175</v>
@@ -34731,13 +34728,13 @@
     </row>
     <row r="1229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1229" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1229" s="18" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="D1229" s="4" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="E1229" s="3" t="s">
         <v>173</v>
@@ -34745,13 +34742,13 @@
     </row>
     <row r="1230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1230" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1230" s="18" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="D1230" s="4" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="E1230" s="3" t="s">
         <v>173</v>
@@ -34759,13 +34756,13 @@
     </row>
     <row r="1231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1231" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1231" s="18" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="D1231" s="4" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="E1231" s="3" t="s">
         <v>173</v>
@@ -34773,13 +34770,13 @@
     </row>
     <row r="1232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1232" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1232" s="18" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="D1232" s="4" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="E1232" s="3" t="s">
         <v>175</v>
@@ -34787,13 +34784,13 @@
     </row>
     <row r="1233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1233" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1233" s="18" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="D1233" s="4" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="E1233" s="3" t="s">
         <v>175</v>
@@ -34801,13 +34798,13 @@
     </row>
     <row r="1234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1234" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1234" s="18" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="D1234" s="4" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="E1234" s="3" t="s">
         <v>175</v>
@@ -34815,13 +34812,13 @@
     </row>
     <row r="1235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1235" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1235" s="18" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="D1235" s="4" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="E1235" s="3" t="s">
         <v>173</v>
@@ -34829,13 +34826,13 @@
     </row>
     <row r="1236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1236" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1236" s="18" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="D1236" s="4" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="E1236" s="3" t="s">
         <v>173</v>
@@ -34843,13 +34840,13 @@
     </row>
     <row r="1237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1237" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1237" s="18" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="D1237" s="4" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="E1237" s="3" t="s">
         <v>173</v>
@@ -34857,13 +34854,13 @@
     </row>
     <row r="1238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1238" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1238" s="18" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="D1238" s="4" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="E1238" s="3" t="s">
         <v>175</v>
@@ -34871,13 +34868,13 @@
     </row>
     <row r="1239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1239" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1239" s="18" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="D1239" s="4" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="E1239" s="3" t="s">
         <v>175</v>
@@ -34885,13 +34882,13 @@
     </row>
     <row r="1240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1240" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1240" s="18" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="D1240" s="4" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="E1240" s="3" t="s">
         <v>175</v>
@@ -34899,13 +34896,13 @@
     </row>
     <row r="1241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1241" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1241" s="18" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="D1241" s="4" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="E1241" s="3" t="s">
         <v>173</v>
@@ -34913,13 +34910,13 @@
     </row>
     <row r="1242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1242" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1242" s="18" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="D1242" s="4" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="E1242" s="3" t="s">
         <v>173</v>
@@ -34927,13 +34924,13 @@
     </row>
     <row r="1243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1243" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1243" s="18" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="D1243" s="4" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="E1243" s="3" t="s">
         <v>173</v>
@@ -34941,13 +34938,13 @@
     </row>
     <row r="1244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1244" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1244" s="18" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="D1244" s="4" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="E1244" s="3" t="s">
         <v>175</v>
@@ -34955,13 +34952,13 @@
     </row>
     <row r="1245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1245" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1245" s="18" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="D1245" s="4" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="E1245" s="3" t="s">
         <v>175</v>
@@ -34969,13 +34966,13 @@
     </row>
     <row r="1246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1246" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1246" s="18" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="D1246" s="4" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="E1246" s="3" t="s">
         <v>173</v>
@@ -34983,13 +34980,13 @@
     </row>
     <row r="1247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1247" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1247" s="18" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="D1247" s="4" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="E1247" s="3" t="s">
         <v>177</v>
@@ -34997,13 +34994,13 @@
     </row>
     <row r="1248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1248" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1248" s="18" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="D1248" s="4" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="E1248" s="3" t="s">
         <v>175</v>
@@ -35011,13 +35008,13 @@
     </row>
     <row r="1249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1249" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1249" s="18" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="D1249" s="4" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="E1249" s="3" t="s">
         <v>173</v>
@@ -35025,13 +35022,13 @@
     </row>
     <row r="1250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1250" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1250" s="18" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="D1250" s="4" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="E1250" s="3" t="s">
         <v>173</v>
@@ -35039,13 +35036,13 @@
     </row>
     <row r="1251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1251" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1251" s="18" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="D1251" s="4" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="E1251" s="3" t="s">
         <v>173</v>
@@ -35053,13 +35050,13 @@
     </row>
     <row r="1252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1252" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1252" s="18" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="D1252" s="4" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="E1252" s="3" t="s">
         <v>173</v>
@@ -35067,13 +35064,13 @@
     </row>
     <row r="1253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1253" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1253" s="18" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="D1253" s="4" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="E1253" s="3" t="s">
         <v>173</v>
@@ -35081,13 +35078,13 @@
     </row>
     <row r="1254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1254" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1254" s="18" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="D1254" s="4" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="E1254" s="3" t="s">
         <v>173</v>
@@ -35095,13 +35092,13 @@
     </row>
     <row r="1255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1255" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1255" s="18" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="D1255" s="4" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="E1255" s="3" t="s">
         <v>175</v>
@@ -35109,13 +35106,13 @@
     </row>
     <row r="1256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1256" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1256" s="18" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="D1256" s="4" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="E1256" s="3" t="s">
         <v>173</v>
@@ -35123,13 +35120,13 @@
     </row>
     <row r="1257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1257" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1257" s="18" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="D1257" s="4" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="E1257" s="3" t="s">
         <v>177</v>
@@ -35137,13 +35134,13 @@
     </row>
     <row r="1258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1258" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1258" s="18" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="D1258" s="4" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="E1258" s="3" t="s">
         <v>175</v>
@@ -35151,13 +35148,13 @@
     </row>
     <row r="1259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1259" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1259" s="18" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="D1259" s="4" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="E1259" s="3" t="s">
         <v>173</v>
@@ -35165,13 +35162,13 @@
     </row>
     <row r="1260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1260" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1260" s="18" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="D1260" s="4" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="E1260" s="3" t="s">
         <v>173</v>
@@ -35179,13 +35176,13 @@
     </row>
     <row r="1261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1261" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1261" s="18" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="D1261" s="4" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="E1261" s="3" t="s">
         <v>173</v>
@@ -35193,13 +35190,13 @@
     </row>
     <row r="1262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1262" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1262" s="18" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="D1262" s="4" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="E1262" s="3" t="s">
         <v>173</v>
@@ -35207,13 +35204,13 @@
     </row>
     <row r="1263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1263" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1263" s="18" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="D1263" s="4" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="E1263" s="3" t="s">
         <v>173</v>
@@ -35221,13 +35218,13 @@
     </row>
     <row r="1264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1264" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1264" s="18" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="D1264" s="4" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="E1264" s="3" t="s">
         <v>173</v>
@@ -35235,13 +35232,13 @@
     </row>
     <row r="1265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1265" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1265" s="18" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="D1265" s="4" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="E1265" s="3" t="s">
         <v>175</v>
@@ -35249,13 +35246,13 @@
     </row>
     <row r="1266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1266" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1266" s="18" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="D1266" s="4" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="E1266" s="3" t="s">
         <v>173</v>
@@ -35263,13 +35260,13 @@
     </row>
     <row r="1267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1267" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1267" s="18" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="D1267" s="4" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="E1267" s="3" t="s">
         <v>175</v>
@@ -35277,13 +35274,13 @@
     </row>
     <row r="1268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1268" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1268" s="18" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="D1268" s="4" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="E1268" s="3" t="s">
         <v>173</v>
@@ -35291,13 +35288,13 @@
     </row>
     <row r="1269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1269" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1269" s="18" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="D1269" s="4" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="E1269" s="3" t="s">
         <v>173</v>
@@ -35305,13 +35302,13 @@
     </row>
     <row r="1270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1270" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1270" s="18" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="D1270" s="4" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="E1270" s="3" t="s">
         <v>173</v>
@@ -35319,13 +35316,13 @@
     </row>
     <row r="1271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1271" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1271" s="18" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="D1271" s="4" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="E1271" s="3" t="s">
         <v>175</v>
@@ -35333,13 +35330,13 @@
     </row>
     <row r="1272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1272" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1272" s="18" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="D1272" s="4" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="E1272" s="3" t="s">
         <v>173</v>
@@ -35347,13 +35344,13 @@
     </row>
     <row r="1273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1273" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1273" s="18" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="D1273" s="4" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="E1273" s="3" t="s">
         <v>175</v>
@@ -35361,13 +35358,13 @@
     </row>
     <row r="1274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1274" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1274" s="18" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="D1274" s="4" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="E1274" s="3" t="s">
         <v>173</v>
@@ -35375,13 +35372,13 @@
     </row>
     <row r="1275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1275" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1275" s="18" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="D1275" s="4" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="E1275" s="3" t="s">
         <v>173</v>
@@ -35389,13 +35386,13 @@
     </row>
     <row r="1276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1276" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1276" s="18" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="D1276" s="4" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="E1276" s="3" t="s">
         <v>173</v>
@@ -35403,13 +35400,13 @@
     </row>
     <row r="1277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1277" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1277" s="18" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="D1277" s="4" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="E1277" s="3" t="s">
         <v>175</v>
@@ -35417,10 +35414,10 @@
     </row>
     <row r="1278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1278" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1278" s="18" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="D1278" s="4" t="s">
         <v>1680</v>
@@ -35431,13 +35428,13 @@
     </row>
     <row r="1279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1279" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1279" s="18" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="D1279" s="4" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="E1279" s="3" t="s">
         <v>175</v>
@@ -35445,13 +35442,13 @@
     </row>
     <row r="1280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1280" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1280" s="18" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="D1280" s="4" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="E1280" s="3" t="s">
         <v>173</v>
@@ -35459,13 +35456,13 @@
     </row>
     <row r="1281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1281" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1281" s="18" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="D1281" s="4" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="E1281" s="3" t="s">
         <v>173</v>
@@ -35473,13 +35470,13 @@
     </row>
     <row r="1282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1282" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1282" s="18" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="D1282" s="4" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="E1282" s="3" t="s">
         <v>173</v>
@@ -35487,13 +35484,13 @@
     </row>
     <row r="1283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1283" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1283" s="18" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="D1283" s="4" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="E1283" s="3" t="s">
         <v>175</v>
@@ -35501,13 +35498,13 @@
     </row>
     <row r="1284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1284" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1284" s="18" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="D1284" s="4" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="E1284" s="3" t="s">
         <v>173</v>
@@ -35515,13 +35512,13 @@
     </row>
     <row r="1285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1285" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1285" s="18" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="D1285" s="4" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="E1285" s="3" t="s">
         <v>175</v>
@@ -35529,13 +35526,13 @@
     </row>
     <row r="1286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1286" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1286" s="18" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="D1286" s="4" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="E1286" s="3" t="s">
         <v>177</v>
@@ -35543,13 +35540,13 @@
     </row>
     <row r="1287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1287" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1287" s="18" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="D1287" s="4" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="E1287" s="3" t="s">
         <v>173</v>
@@ -35557,13 +35554,13 @@
     </row>
     <row r="1288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1288" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1288" s="18" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="D1288" s="4" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="E1288" s="3" t="s">
         <v>173</v>
@@ -35571,13 +35568,13 @@
     </row>
     <row r="1289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1289" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1289" s="18" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="D1289" s="4" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="E1289" s="3" t="s">
         <v>173</v>
@@ -35585,13 +35582,13 @@
     </row>
     <row r="1290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1290" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1290" s="18" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="D1290" s="4" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="E1290" s="3" t="s">
         <v>173</v>
@@ -35599,13 +35596,13 @@
     </row>
     <row r="1291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1291" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1291" s="18" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="D1291" s="4" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="E1291" s="3" t="s">
         <v>173</v>
@@ -35613,13 +35610,13 @@
     </row>
     <row r="1292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1292" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1292" s="18" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="D1292" s="4" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="E1292" s="3" t="s">
         <v>173</v>
@@ -35627,13 +35624,13 @@
     </row>
     <row r="1293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1293" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1293" s="18" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="D1293" s="4" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="E1293" s="3" t="s">
         <v>175</v>
@@ -35641,13 +35638,13 @@
     </row>
     <row r="1294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1294" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1294" s="18" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="D1294" s="4" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="E1294" s="3" t="s">
         <v>173</v>
@@ -35655,13 +35652,13 @@
     </row>
     <row r="1295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1295" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1295" s="18" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="D1295" s="4" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="E1295" s="3" t="s">
         <v>175</v>
@@ -35669,13 +35666,13 @@
     </row>
     <row r="1296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1296" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1296" s="18" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="D1296" s="4" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="E1296" s="3" t="s">
         <v>173</v>
@@ -35683,13 +35680,13 @@
     </row>
     <row r="1297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1297" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1297" s="18" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="D1297" s="4" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="E1297" s="3" t="s">
         <v>173</v>
@@ -35697,13 +35694,13 @@
     </row>
     <row r="1298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1298" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1298" s="18" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="D1298" s="4" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="E1298" s="3" t="s">
         <v>173</v>
@@ -35711,13 +35708,13 @@
     </row>
     <row r="1299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1299" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1299" s="18" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="D1299" s="4" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="E1299" s="3" t="s">
         <v>175</v>
@@ -35725,13 +35722,13 @@
     </row>
     <row r="1300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1300" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1300" s="18" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="D1300" s="4" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="E1300" s="3" t="s">
         <v>173</v>
@@ -35739,13 +35736,13 @@
     </row>
     <row r="1301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1301" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1301" s="18" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="D1301" s="4" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="E1301" s="3" t="s">
         <v>175</v>
@@ -35753,13 +35750,13 @@
     </row>
     <row r="1302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1302" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1302" s="18" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="D1302" s="4" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="E1302" s="3" t="s">
         <v>177</v>
@@ -35767,13 +35764,13 @@
     </row>
     <row r="1303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1303" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1303" s="18" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="D1303" s="4" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="E1303" s="3" t="s">
         <v>173</v>
@@ -35781,13 +35778,13 @@
     </row>
     <row r="1304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1304" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1304" s="18" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="D1304" s="4" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="E1304" s="3" t="s">
         <v>173</v>
@@ -35795,13 +35792,13 @@
     </row>
     <row r="1305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1305" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1305" s="18" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="D1305" s="4" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="E1305" s="3" t="s">
         <v>173</v>
@@ -35809,13 +35806,13 @@
     </row>
     <row r="1306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1306" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1306" s="18" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="D1306" s="4" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="E1306" s="3" t="s">
         <v>173</v>
@@ -35823,13 +35820,13 @@
     </row>
     <row r="1307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1307" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1307" s="18" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="D1307" s="4" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="E1307" s="3" t="s">
         <v>173</v>
@@ -35837,13 +35834,13 @@
     </row>
     <row r="1308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1308" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1308" s="18" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="D1308" s="4" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="E1308" s="3" t="s">
         <v>173</v>
@@ -35851,13 +35848,13 @@
     </row>
     <row r="1309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1309" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1309" s="18" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="D1309" s="4" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="E1309" s="3" t="s">
         <v>175</v>
@@ -35865,13 +35862,13 @@
     </row>
     <row r="1310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1310" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1310" s="18" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="D1310" s="4" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="E1310" s="3" t="s">
         <v>173</v>
@@ -35879,13 +35876,13 @@
     </row>
     <row r="1311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1311" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1311" s="18" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="D1311" s="4" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="E1311" s="3" t="s">
         <v>175</v>
@@ -35893,13 +35890,13 @@
     </row>
     <row r="1312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1312" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1312" s="18" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="D1312" s="4" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="E1312" s="3" t="s">
         <v>177</v>
@@ -35907,13 +35904,13 @@
     </row>
     <row r="1313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1313" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1313" s="18" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="D1313" s="4" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="E1313" s="3" t="s">
         <v>173</v>
@@ -35921,13 +35918,13 @@
     </row>
     <row r="1314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1314" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1314" s="18" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="D1314" s="4" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="E1314" s="3" t="s">
         <v>173</v>
@@ -35935,13 +35932,13 @@
     </row>
     <row r="1315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1315" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1315" s="18" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="D1315" s="4" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="E1315" s="3" t="s">
         <v>173</v>
@@ -35949,13 +35946,13 @@
     </row>
     <row r="1316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1316" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1316" s="18" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="D1316" s="4" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="E1316" s="3" t="s">
         <v>173</v>
@@ -35963,13 +35960,13 @@
     </row>
     <row r="1317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1317" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1317" s="18" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="D1317" s="4" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="E1317" s="3" t="s">
         <v>173</v>
@@ -35977,13 +35974,13 @@
     </row>
     <row r="1318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1318" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1318" s="18" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="D1318" s="4" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="E1318" s="3" t="s">
         <v>173</v>
@@ -35991,13 +35988,13 @@
     </row>
     <row r="1319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1319" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1319" s="18" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="D1319" s="4" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="E1319" s="3" t="s">
         <v>175</v>
@@ -36005,13 +36002,13 @@
     </row>
     <row r="1320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1320" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1320" s="18" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="D1320" s="4" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="E1320" s="3" t="s">
         <v>173</v>
@@ -36019,13 +36016,13 @@
     </row>
     <row r="1321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1321" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1321" s="18" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="D1321" s="4" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="E1321" s="3" t="s">
         <v>175</v>
@@ -36033,13 +36030,13 @@
     </row>
     <row r="1322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1322" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1322" s="18" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="D1322" s="4" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="E1322" s="3" t="s">
         <v>173</v>
@@ -36047,13 +36044,13 @@
     </row>
     <row r="1323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1323" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1323" s="18" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="D1323" s="4" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="E1323" s="3" t="s">
         <v>173</v>
@@ -36061,13 +36058,13 @@
     </row>
     <row r="1324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1324" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1324" s="18" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="D1324" s="4" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="E1324" s="3" t="s">
         <v>173</v>
@@ -36075,13 +36072,13 @@
     </row>
     <row r="1325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1325" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1325" s="18" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="D1325" s="4" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="E1325" s="3" t="s">
         <v>175</v>
@@ -36089,13 +36086,13 @@
     </row>
     <row r="1326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1326" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1326" s="18" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="D1326" s="4" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="E1326" s="3" t="s">
         <v>173</v>
@@ -36103,13 +36100,13 @@
     </row>
     <row r="1327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1327" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1327" s="18" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="D1327" s="4" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="E1327" s="3" t="s">
         <v>175</v>
@@ -36117,13 +36114,13 @@
     </row>
     <row r="1328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1328" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1328" s="18" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="D1328" s="4" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="E1328" s="3" t="s">
         <v>177</v>
@@ -36131,13 +36128,13 @@
     </row>
     <row r="1329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1329" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1329" s="18" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="D1329" s="4" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="E1329" s="3" t="s">
         <v>173</v>
@@ -36145,13 +36142,13 @@
     </row>
     <row r="1330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1330" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1330" s="18" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="D1330" s="4" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="E1330" s="3" t="s">
         <v>173</v>
@@ -36159,13 +36156,13 @@
     </row>
     <row r="1331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1331" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1331" s="18" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="D1331" s="4" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="E1331" s="3" t="s">
         <v>173</v>
@@ -36173,13 +36170,13 @@
     </row>
     <row r="1332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1332" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1332" s="18" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="D1332" s="4" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="E1332" s="3" t="s">
         <v>173</v>
@@ -36187,13 +36184,13 @@
     </row>
     <row r="1333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1333" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1333" s="18" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="D1333" s="4" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="E1333" s="3" t="s">
         <v>173</v>
@@ -36201,13 +36198,13 @@
     </row>
     <row r="1334" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1334" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1334" s="18" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="D1334" s="4" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="E1334" s="3" t="s">
         <v>173</v>
@@ -36215,13 +36212,13 @@
     </row>
     <row r="1335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1335" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1335" s="18" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="D1335" s="4" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="E1335" s="3" t="s">
         <v>175</v>
@@ -36229,13 +36226,13 @@
     </row>
     <row r="1336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1336" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1336" s="18" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="D1336" s="4" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="E1336" s="3" t="s">
         <v>173</v>
@@ -36243,13 +36240,13 @@
     </row>
     <row r="1337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1337" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1337" s="18" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="D1337" s="4" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="E1337" s="3" t="s">
         <v>175</v>
@@ -36257,13 +36254,13 @@
     </row>
     <row r="1338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1338" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1338" s="18" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="D1338" s="4" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="E1338" s="3" t="s">
         <v>177</v>
@@ -36271,13 +36268,13 @@
     </row>
     <row r="1339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1339" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1339" s="18" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="D1339" s="4" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="E1339" s="3" t="s">
         <v>173</v>
@@ -36285,13 +36282,13 @@
     </row>
     <row r="1340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1340" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1340" s="18" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="D1340" s="4" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="E1340" s="3" t="s">
         <v>173</v>
@@ -36299,13 +36296,13 @@
     </row>
     <row r="1341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1341" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1341" s="18" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="D1341" s="4" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="E1341" s="3" t="s">
         <v>173</v>
@@ -36313,13 +36310,13 @@
     </row>
     <row r="1342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1342" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1342" s="18" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="D1342" s="4" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="E1342" s="3" t="s">
         <v>173</v>
@@ -36327,13 +36324,13 @@
     </row>
     <row r="1343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1343" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1343" s="18" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="D1343" s="4" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="E1343" s="3" t="s">
         <v>173</v>
@@ -36341,13 +36338,13 @@
     </row>
     <row r="1344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1344" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1344" s="18" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="D1344" s="4" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="E1344" s="3" t="s">
         <v>173</v>
@@ -36355,13 +36352,13 @@
     </row>
     <row r="1345" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1345" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1345" s="18" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="D1345" s="4" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E1345" s="3" t="s">
         <v>175</v>
@@ -36369,13 +36366,13 @@
     </row>
     <row r="1346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1346" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1346" s="18" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="D1346" s="4" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="E1346" s="3" t="s">
         <v>173</v>
@@ -36383,13 +36380,13 @@
     </row>
     <row r="1347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1347" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1347" s="18" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="D1347" s="4" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="E1347" s="3" t="s">
         <v>175</v>
@@ -36397,13 +36394,13 @@
     </row>
     <row r="1348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1348" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1348" s="18" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="D1348" s="4" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="E1348" s="3" t="s">
         <v>175</v>
@@ -36411,13 +36408,13 @@
     </row>
     <row r="1349" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1349" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1349" s="18" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="D1349" s="4" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="E1349" s="3" t="s">
         <v>173</v>
@@ -36425,13 +36422,13 @@
     </row>
     <row r="1350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1350" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1350" s="18" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="D1350" s="4" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="E1350" s="3" t="s">
         <v>173</v>
@@ -36439,13 +36436,13 @@
     </row>
     <row r="1351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1351" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1351" s="18" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="D1351" s="4" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="E1351" s="3" t="s">
         <v>173</v>
@@ -36453,13 +36450,13 @@
     </row>
     <row r="1352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1352" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1352" s="18" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="D1352" s="4" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="E1352" s="3" t="s">
         <v>175</v>
@@ -36467,13 +36464,13 @@
     </row>
     <row r="1353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1353" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1353" s="18" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="D1353" s="4" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="E1353" s="3" t="s">
         <v>175</v>
@@ -36481,13 +36478,13 @@
     </row>
     <row r="1354" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1354" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1354" s="18" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="D1354" s="4" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="E1354" s="3" t="s">
         <v>175</v>
@@ -36495,13 +36492,13 @@
     </row>
     <row r="1355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1355" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1355" s="18" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="D1355" s="4" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="E1355" s="3" t="s">
         <v>175</v>
@@ -36509,13 +36506,13 @@
     </row>
     <row r="1356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1356" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1356" s="18" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="D1356" s="4" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="E1356" s="3" t="s">
         <v>173</v>
@@ -36523,13 +36520,13 @@
     </row>
     <row r="1357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1357" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1357" s="18" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="D1357" s="4" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="E1357" s="3" t="s">
         <v>173</v>
@@ -36537,13 +36534,13 @@
     </row>
     <row r="1358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1358" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1358" s="18" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="D1358" s="4" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="E1358" s="3" t="s">
         <v>175</v>
@@ -36551,13 +36548,13 @@
     </row>
     <row r="1359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1359" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1359" s="18" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="D1359" s="4" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="E1359" s="3" t="s">
         <v>175</v>
@@ -36565,13 +36562,13 @@
     </row>
     <row r="1360" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1360" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1360" s="18" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="D1360" s="4" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="E1360" s="3" t="s">
         <v>173</v>
@@ -36579,13 +36576,13 @@
     </row>
     <row r="1361" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1361" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1361" s="18" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="D1361" s="4" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="E1361" s="3" t="s">
         <v>173</v>
@@ -36593,13 +36590,13 @@
     </row>
     <row r="1362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1362" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1362" s="18" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="D1362" s="4" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="E1362" s="3" t="s">
         <v>173</v>
@@ -36607,13 +36604,13 @@
     </row>
     <row r="1363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1363" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1363" s="18" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="D1363" s="4" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="E1363" s="3" t="s">
         <v>175</v>
@@ -36621,13 +36618,13 @@
     </row>
     <row r="1364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1364" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1364" s="18" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="D1364" s="4" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="E1364" s="3" t="s">
         <v>175</v>
@@ -36635,13 +36632,13 @@
     </row>
     <row r="1365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1365" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1365" s="18" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="D1365" s="4" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="E1365" s="3" t="s">
         <v>175</v>
@@ -36649,13 +36646,13 @@
     </row>
     <row r="1366" spans="1:5" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1366" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1366" s="18" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="D1366" s="4" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="E1366" s="3" t="s">
         <v>175</v>
@@ -36663,13 +36660,13 @@
     </row>
     <row r="1367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1367" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1367" s="18" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="D1367" s="4" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="E1367" s="3" t="s">
         <v>173</v>
@@ -36677,13 +36674,13 @@
     </row>
     <row r="1368" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1368" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B1368" s="18" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="D1368" s="4" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="E1368" s="3" t="s">
         <v>173</v>
@@ -36694,10 +36691,10 @@
         <v>33</v>
       </c>
       <c r="B1369" s="18" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D1369" s="4" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="E1369" s="3" t="s">
         <v>177</v>
@@ -36708,10 +36705,10 @@
         <v>33</v>
       </c>
       <c r="B1370" s="18" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="D1370" s="4" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="E1370" s="3" t="s">
         <v>175</v>
@@ -36722,10 +36719,10 @@
         <v>33</v>
       </c>
       <c r="B1371" s="18" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="D1371" s="4" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="E1371" s="3" t="s">
         <v>175</v>
@@ -36736,10 +36733,10 @@
         <v>33</v>
       </c>
       <c r="B1372" s="18" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="D1372" s="4" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="E1372" s="3" t="s">
         <v>175</v>
@@ -36750,10 +36747,10 @@
         <v>33</v>
       </c>
       <c r="B1373" s="18" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="D1373" s="4" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="E1373" s="3" t="s">
         <v>175</v>
@@ -36764,10 +36761,10 @@
         <v>33</v>
       </c>
       <c r="B1374" s="18" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="D1374" s="4" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="E1374" s="3" t="s">
         <v>175</v>
@@ -36778,10 +36775,10 @@
         <v>33</v>
       </c>
       <c r="B1375" s="18" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="D1375" s="4" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="E1375" s="3" t="s">
         <v>175</v>
@@ -36792,10 +36789,10 @@
         <v>33</v>
       </c>
       <c r="B1376" s="18" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="D1376" s="4" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="E1376" s="3" t="s">
         <v>175</v>
@@ -36806,10 +36803,10 @@
         <v>33</v>
       </c>
       <c r="B1377" s="18" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="D1377" s="4" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="E1377" s="3" t="s">
         <v>175</v>
@@ -36820,10 +36817,10 @@
         <v>33</v>
       </c>
       <c r="B1378" s="18" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D1378" s="4" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="E1378" s="3" t="s">
         <v>177</v>
@@ -36834,10 +36831,10 @@
         <v>33</v>
       </c>
       <c r="B1379" s="18" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D1379" s="4" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="E1379" s="3" t="s">
         <v>175</v>
@@ -36848,10 +36845,10 @@
         <v>33</v>
       </c>
       <c r="B1380" s="18" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D1380" s="4" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="E1380" s="3" t="s">
         <v>175</v>
@@ -36862,10 +36859,10 @@
         <v>33</v>
       </c>
       <c r="B1381" s="18" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="D1381" s="4" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="E1381" s="3" t="s">
         <v>175</v>
@@ -36876,10 +36873,10 @@
         <v>33</v>
       </c>
       <c r="B1382" s="18" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="D1382" s="4" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="E1382" s="3" t="s">
         <v>175</v>
@@ -36890,10 +36887,10 @@
         <v>33</v>
       </c>
       <c r="B1383" s="18" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D1383" s="4" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="E1383" s="3" t="s">
         <v>175</v>
@@ -36904,10 +36901,10 @@
         <v>33</v>
       </c>
       <c r="B1384" s="18" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D1384" s="4" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="E1384" s="3" t="s">
         <v>175</v>
@@ -36918,10 +36915,10 @@
         <v>33</v>
       </c>
       <c r="B1385" s="18" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D1385" s="4" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="E1385" s="3" t="s">
         <v>175</v>
@@ -36932,10 +36929,10 @@
         <v>33</v>
       </c>
       <c r="B1386" s="18" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="D1386" s="4" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="E1386" s="3" t="s">
         <v>175</v>
@@ -36946,10 +36943,10 @@
         <v>33</v>
       </c>
       <c r="B1387" s="18" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="D1387" s="4" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="E1387" s="3" t="s">
         <v>177</v>
@@ -36960,10 +36957,10 @@
         <v>33</v>
       </c>
       <c r="B1388" s="18" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="D1388" s="4" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="E1388" s="3" t="s">
         <v>175</v>
@@ -36974,10 +36971,10 @@
         <v>33</v>
       </c>
       <c r="B1389" s="18" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="D1389" s="4" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="E1389" s="3" t="s">
         <v>175</v>
@@ -36988,10 +36985,10 @@
         <v>33</v>
       </c>
       <c r="B1390" s="18" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="D1390" s="4" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="E1390" s="3" t="s">
         <v>175</v>
@@ -37002,10 +36999,10 @@
         <v>33</v>
       </c>
       <c r="B1391" s="18" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="D1391" s="4" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="E1391" s="3" t="s">
         <v>175</v>
@@ -37016,10 +37013,10 @@
         <v>33</v>
       </c>
       <c r="B1392" s="18" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="D1392" s="4" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="E1392" s="3" t="s">
         <v>175</v>
@@ -37030,10 +37027,10 @@
         <v>33</v>
       </c>
       <c r="B1393" s="18" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="D1393" s="4" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="E1393" s="3" t="s">
         <v>175</v>
@@ -37044,10 +37041,10 @@
         <v>33</v>
       </c>
       <c r="B1394" s="18" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="D1394" s="4" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="E1394" s="3" t="s">
         <v>175</v>
@@ -37058,10 +37055,10 @@
         <v>33</v>
       </c>
       <c r="B1395" s="18" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="D1395" s="4" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="E1395" s="3" t="s">
         <v>175</v>
@@ -62615,13 +62612,13 @@
         <v>3048</v>
       </c>
       <c r="B2130" s="18" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="C2130" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2130" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2131" spans="1:4" x14ac:dyDescent="0.3">
@@ -62629,10 +62626,10 @@
         <v>3048</v>
       </c>
       <c r="B2131" s="18" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="C2131" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2132" spans="1:4" x14ac:dyDescent="0.3">
@@ -62640,7 +62637,7 @@
         <v>3048</v>
       </c>
       <c r="B2132" s="18" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="C2132" s="16" t="s">
         <v>2255</v>
@@ -62651,7 +62648,7 @@
         <v>3048</v>
       </c>
       <c r="B2133" s="18" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="C2133" s="16" t="s">
         <v>2185</v>
@@ -62662,7 +62659,7 @@
         <v>3048</v>
       </c>
       <c r="B2134" s="18" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="C2134" s="16" t="s">
         <v>2256</v>
@@ -62673,13 +62670,13 @@
         <v>3048</v>
       </c>
       <c r="B2135" s="18" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C2135" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2135" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2136" spans="1:4" x14ac:dyDescent="0.3">
@@ -62687,10 +62684,10 @@
         <v>3048</v>
       </c>
       <c r="B2136" s="18" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C2136" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2137" spans="1:4" x14ac:dyDescent="0.3">
@@ -62698,7 +62695,7 @@
         <v>3048</v>
       </c>
       <c r="B2137" s="18" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C2137" s="16" t="s">
         <v>2255</v>
@@ -62709,7 +62706,7 @@
         <v>3048</v>
       </c>
       <c r="B2138" s="18" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C2138" s="16" t="s">
         <v>2185</v>
@@ -62720,7 +62717,7 @@
         <v>3048</v>
       </c>
       <c r="B2139" s="18" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C2139" s="16" t="s">
         <v>2256</v>
@@ -62731,13 +62728,13 @@
         <v>3048</v>
       </c>
       <c r="B2140" s="18" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="C2140" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2140" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2141" spans="1:4" x14ac:dyDescent="0.3">
@@ -62745,10 +62742,10 @@
         <v>3048</v>
       </c>
       <c r="B2141" s="18" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="C2141" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2142" spans="1:4" x14ac:dyDescent="0.3">
@@ -62756,7 +62753,7 @@
         <v>3048</v>
       </c>
       <c r="B2142" s="18" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="C2142" s="16" t="s">
         <v>2255</v>
@@ -62767,7 +62764,7 @@
         <v>3048</v>
       </c>
       <c r="B2143" s="18" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="C2143" s="16" t="s">
         <v>2185</v>
@@ -62778,7 +62775,7 @@
         <v>3048</v>
       </c>
       <c r="B2144" s="18" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="C2144" s="16" t="s">
         <v>2256</v>
@@ -62789,13 +62786,13 @@
         <v>3048</v>
       </c>
       <c r="B2145" s="18" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C2145" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2145" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2146" spans="1:4" x14ac:dyDescent="0.3">
@@ -62803,10 +62800,10 @@
         <v>3048</v>
       </c>
       <c r="B2146" s="18" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C2146" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2147" spans="1:4" x14ac:dyDescent="0.3">
@@ -62814,7 +62811,7 @@
         <v>3048</v>
       </c>
       <c r="B2147" s="18" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C2147" s="16" t="s">
         <v>2255</v>
@@ -62825,7 +62822,7 @@
         <v>3048</v>
       </c>
       <c r="B2148" s="18" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C2148" s="16" t="s">
         <v>2185</v>
@@ -62836,7 +62833,7 @@
         <v>3048</v>
       </c>
       <c r="B2149" s="18" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C2149" s="16" t="s">
         <v>2256</v>
@@ -62847,13 +62844,13 @@
         <v>3048</v>
       </c>
       <c r="B2150" s="18" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="C2150" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2150" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2151" spans="1:4" x14ac:dyDescent="0.3">
@@ -62861,10 +62858,10 @@
         <v>3048</v>
       </c>
       <c r="B2151" s="18" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="C2151" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2152" spans="1:4" x14ac:dyDescent="0.3">
@@ -62872,7 +62869,7 @@
         <v>3048</v>
       </c>
       <c r="B2152" s="18" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="C2152" s="16" t="s">
         <v>2255</v>
@@ -62883,7 +62880,7 @@
         <v>3048</v>
       </c>
       <c r="B2153" s="18" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="C2153" s="16" t="s">
         <v>2185</v>
@@ -62894,7 +62891,7 @@
         <v>3048</v>
       </c>
       <c r="B2154" s="18" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="C2154" s="16" t="s">
         <v>2256</v>
@@ -62905,13 +62902,13 @@
         <v>3048</v>
       </c>
       <c r="B2155" s="18" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C2155" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2155" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2156" spans="1:4" x14ac:dyDescent="0.3">
@@ -62919,10 +62916,10 @@
         <v>3048</v>
       </c>
       <c r="B2156" s="18" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C2156" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2157" spans="1:4" x14ac:dyDescent="0.3">
@@ -62930,7 +62927,7 @@
         <v>3048</v>
       </c>
       <c r="B2157" s="18" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C2157" s="16" t="s">
         <v>2255</v>
@@ -62941,7 +62938,7 @@
         <v>3048</v>
       </c>
       <c r="B2158" s="18" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C2158" s="16" t="s">
         <v>2185</v>
@@ -62952,7 +62949,7 @@
         <v>3048</v>
       </c>
       <c r="B2159" s="18" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C2159" s="16" t="s">
         <v>2256</v>
@@ -62963,13 +62960,13 @@
         <v>3048</v>
       </c>
       <c r="B2160" s="18" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C2160" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2160" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2161" spans="1:4" x14ac:dyDescent="0.3">
@@ -62977,10 +62974,10 @@
         <v>3048</v>
       </c>
       <c r="B2161" s="18" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C2161" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2162" spans="1:4" x14ac:dyDescent="0.3">
@@ -62988,7 +62985,7 @@
         <v>3048</v>
       </c>
       <c r="B2162" s="18" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C2162" s="16" t="s">
         <v>2255</v>
@@ -62999,7 +62996,7 @@
         <v>3048</v>
       </c>
       <c r="B2163" s="18" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C2163" s="16" t="s">
         <v>2185</v>
@@ -63010,7 +63007,7 @@
         <v>3048</v>
       </c>
       <c r="B2164" s="18" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C2164" s="16" t="s">
         <v>2256</v>
@@ -63021,13 +63018,13 @@
         <v>3048</v>
       </c>
       <c r="B2165" s="18" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="C2165" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2165" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2166" spans="1:4" x14ac:dyDescent="0.3">
@@ -63035,10 +63032,10 @@
         <v>3048</v>
       </c>
       <c r="B2166" s="18" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="C2166" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2167" spans="1:4" x14ac:dyDescent="0.3">
@@ -63046,7 +63043,7 @@
         <v>3048</v>
       </c>
       <c r="B2167" s="18" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="C2167" s="16" t="s">
         <v>2255</v>
@@ -63057,7 +63054,7 @@
         <v>3048</v>
       </c>
       <c r="B2168" s="18" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="C2168" s="16" t="s">
         <v>2185</v>
@@ -63068,7 +63065,7 @@
         <v>3048</v>
       </c>
       <c r="B2169" s="18" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="C2169" s="16" t="s">
         <v>2256</v>
@@ -63079,13 +63076,13 @@
         <v>3048</v>
       </c>
       <c r="B2170" s="18" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C2170" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2170" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2171" spans="1:4" x14ac:dyDescent="0.3">
@@ -63093,10 +63090,10 @@
         <v>3048</v>
       </c>
       <c r="B2171" s="18" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C2171" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2172" spans="1:4" x14ac:dyDescent="0.3">
@@ -63104,7 +63101,7 @@
         <v>3048</v>
       </c>
       <c r="B2172" s="18" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C2172" s="16" t="s">
         <v>2255</v>
@@ -63115,7 +63112,7 @@
         <v>3048</v>
       </c>
       <c r="B2173" s="18" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C2173" s="16" t="s">
         <v>2185</v>
@@ -63126,7 +63123,7 @@
         <v>3048</v>
       </c>
       <c r="B2174" s="18" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C2174" s="16" t="s">
         <v>2256</v>
@@ -63137,13 +63134,13 @@
         <v>3048</v>
       </c>
       <c r="B2175" s="18" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="C2175" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2175" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2176" spans="1:4" x14ac:dyDescent="0.3">
@@ -63151,10 +63148,10 @@
         <v>3048</v>
       </c>
       <c r="B2176" s="18" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="C2176" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2177" spans="1:4" x14ac:dyDescent="0.3">
@@ -63162,7 +63159,7 @@
         <v>3048</v>
       </c>
       <c r="B2177" s="18" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="C2177" s="16" t="s">
         <v>2255</v>
@@ -63173,7 +63170,7 @@
         <v>3048</v>
       </c>
       <c r="B2178" s="18" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="C2178" s="16" t="s">
         <v>2185</v>
@@ -63184,7 +63181,7 @@
         <v>3048</v>
       </c>
       <c r="B2179" s="18" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="C2179" s="16" t="s">
         <v>2256</v>
@@ -63195,13 +63192,13 @@
         <v>3048</v>
       </c>
       <c r="B2180" s="18" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="C2180" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2180" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2181" spans="1:4" x14ac:dyDescent="0.3">
@@ -63209,10 +63206,10 @@
         <v>3048</v>
       </c>
       <c r="B2181" s="18" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="C2181" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2182" spans="1:4" x14ac:dyDescent="0.3">
@@ -63220,7 +63217,7 @@
         <v>3048</v>
       </c>
       <c r="B2182" s="18" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="C2182" s="16" t="s">
         <v>2255</v>
@@ -63231,7 +63228,7 @@
         <v>3048</v>
       </c>
       <c r="B2183" s="18" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="C2183" s="16" t="s">
         <v>2185</v>
@@ -63242,7 +63239,7 @@
         <v>3048</v>
       </c>
       <c r="B2184" s="18" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="C2184" s="16" t="s">
         <v>2256</v>
@@ -63253,13 +63250,13 @@
         <v>3048</v>
       </c>
       <c r="B2185" s="18" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="C2185" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2185" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2186" spans="1:4" x14ac:dyDescent="0.3">
@@ -63267,10 +63264,10 @@
         <v>3048</v>
       </c>
       <c r="B2186" s="18" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="C2186" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2187" spans="1:4" x14ac:dyDescent="0.3">
@@ -63278,7 +63275,7 @@
         <v>3048</v>
       </c>
       <c r="B2187" s="18" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="C2187" s="16" t="s">
         <v>2255</v>
@@ -63289,7 +63286,7 @@
         <v>3048</v>
       </c>
       <c r="B2188" s="18" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="C2188" s="16" t="s">
         <v>2185</v>
@@ -63300,7 +63297,7 @@
         <v>3048</v>
       </c>
       <c r="B2189" s="18" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="C2189" s="16" t="s">
         <v>2256</v>
@@ -63311,13 +63308,13 @@
         <v>3048</v>
       </c>
       <c r="B2190" s="18" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C2190" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2190" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2191" spans="1:4" x14ac:dyDescent="0.3">
@@ -63325,10 +63322,10 @@
         <v>3048</v>
       </c>
       <c r="B2191" s="18" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C2191" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2192" spans="1:4" x14ac:dyDescent="0.3">
@@ -63336,7 +63333,7 @@
         <v>3048</v>
       </c>
       <c r="B2192" s="18" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C2192" s="16" t="s">
         <v>2255</v>
@@ -63347,7 +63344,7 @@
         <v>3048</v>
       </c>
       <c r="B2193" s="18" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C2193" s="16" t="s">
         <v>2185</v>
@@ -63358,7 +63355,7 @@
         <v>3048</v>
       </c>
       <c r="B2194" s="18" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C2194" s="16" t="s">
         <v>2256</v>
@@ -63369,13 +63366,13 @@
         <v>3048</v>
       </c>
       <c r="B2195" s="18" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="C2195" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2195" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2196" spans="1:4" x14ac:dyDescent="0.3">
@@ -63383,10 +63380,10 @@
         <v>3048</v>
       </c>
       <c r="B2196" s="18" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="C2196" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2197" spans="1:4" x14ac:dyDescent="0.3">
@@ -63394,7 +63391,7 @@
         <v>3048</v>
       </c>
       <c r="B2197" s="18" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="C2197" s="16" t="s">
         <v>2255</v>
@@ -63405,7 +63402,7 @@
         <v>3048</v>
       </c>
       <c r="B2198" s="18" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="C2198" s="16" t="s">
         <v>2185</v>
@@ -63416,7 +63413,7 @@
         <v>3048</v>
       </c>
       <c r="B2199" s="18" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="C2199" s="16" t="s">
         <v>2256</v>
@@ -63427,13 +63424,13 @@
         <v>3048</v>
       </c>
       <c r="B2200" s="18" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C2200" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2200" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2201" spans="1:4" x14ac:dyDescent="0.3">
@@ -63441,10 +63438,10 @@
         <v>3048</v>
       </c>
       <c r="B2201" s="18" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C2201" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2202" spans="1:4" x14ac:dyDescent="0.3">
@@ -63452,7 +63449,7 @@
         <v>3048</v>
       </c>
       <c r="B2202" s="18" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C2202" s="16" t="s">
         <v>2255</v>
@@ -63463,7 +63460,7 @@
         <v>3048</v>
       </c>
       <c r="B2203" s="18" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C2203" s="16" t="s">
         <v>2185</v>
@@ -63474,7 +63471,7 @@
         <v>3048</v>
       </c>
       <c r="B2204" s="18" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C2204" s="16" t="s">
         <v>2256</v>
@@ -63485,13 +63482,13 @@
         <v>3048</v>
       </c>
       <c r="B2205" s="18" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="C2205" s="16" t="s">
         <v>2188</v>
       </c>
       <c r="D2205" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="2206" spans="1:4" x14ac:dyDescent="0.3">
@@ -63499,10 +63496,10 @@
         <v>3048</v>
       </c>
       <c r="B2206" s="18" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="C2206" s="16" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="2207" spans="1:4" x14ac:dyDescent="0.3">
@@ -63510,7 +63507,7 @@
         <v>3048</v>
       </c>
       <c r="B2207" s="18" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="C2207" s="16" t="s">
         <v>2255</v>
@@ -63521,7 +63518,7 @@
         <v>3048</v>
       </c>
       <c r="B2208" s="18" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="C2208" s="16" t="s">
         <v>2185</v>
@@ -63532,7 +63529,7 @@
         <v>3048</v>
       </c>
       <c r="B2209" s="18" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="C2209" s="16" t="s">
         <v>2256</v>
@@ -63540,450 +63537,450 @@
     </row>
     <row r="2210" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A2210" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2210" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2210" s="16" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="D2210" s="4" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="2211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2211" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2211" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2211" s="16" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="2212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2212" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2212" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2212" s="16" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="2213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2213" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2213" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2213" s="16" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="2214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2214" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2214" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2214" s="16" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="2215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2215" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2215" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2215" s="16" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="2216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2216" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2216" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2216" s="16" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="2217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2217" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2217" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2217" s="16" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="2218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2218" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2218" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2218" s="16" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="2219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2219" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2219" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2219" s="16" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="2220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2220" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2220" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2220" s="16" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="2221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2221" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2221" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2221" s="16" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="2222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2222" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2222" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2222" s="16" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="2223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2223" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2223" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2223" s="16" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="2224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2224" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2224" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2224" s="16" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="2225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2225" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2225" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2225" s="16" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="2226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2226" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2226" s="18" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C2226" s="16" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="2227" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2227" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2227" s="18" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="C2227" s="16" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="D2227" s="4" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="2228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2228" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2228" s="18" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="C2228" s="16" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="2229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2229" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2229" s="18" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="C2229" s="16" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="2230" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2230" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2230" s="18" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="C2230" s="16" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="D2230" s="4" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="2231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2231" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2231" s="18" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="C2231" s="16" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="2232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2232" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2232" s="18" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="C2232" s="16" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="2233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2233" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2233" s="18" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="C2233" s="16" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="2234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2234" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2234" s="18" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="C2234" s="16" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="D2234" s="4" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="2235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2235" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2235" s="18" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="C2235" s="16" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="2236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2236" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2236" s="18" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="C2236" s="16" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="D2236" s="4" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="2237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2237" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2237" s="18" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="C2237" s="16" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="2238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2238" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2238" s="18" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="C2238" s="16" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="D2238" s="4" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="2239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2239" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2239" s="18" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="C2239" s="16" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="2240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2240" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2240" s="18" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C2240" s="16" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="D2240" s="4" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="2241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2241" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2241" s="18" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C2241" s="16" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="2242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2242" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2242" s="18" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="C2242" s="16" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="D2242" s="4" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="2243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2243" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2243" s="18" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="C2243" s="16" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="2244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2244" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2244" s="18" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="C2244" s="16" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="D2244" s="4" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="2245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2245" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2245" s="18" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="C2245" s="16" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="2246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2246" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2246" s="18" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="C2246" s="16" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="D2246" s="4" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="2247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2247" s="3" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="B2247" s="18" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="C2247" s="16" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
     </row>
   </sheetData>
